--- a/outputs/marine_equipment/Арматура_по_размеру.xlsx
+++ b/outputs/marine_equipment/Арматура_по_размеру.xlsx
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G17" s="9" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G23" s="9" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G24" s="9" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G29" s="9" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G62" s="9" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G147" s="9" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G162" s="9" t="n">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G280" s="9" t="n">

--- a/outputs/marine_equipment/Арматура_по_размеру.xlsx
+++ b/outputs/marine_equipment/Арматура_по_размеру.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="От большего к меньшему" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Сводка по диаметрам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="По типам и диаметрам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="От большего к меньшему" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка по диаметрам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По типам и диаметрам" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'От большего к меньшему'!$A$4:$O$296</definedName>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>286 позиций, 2902 шт, 27.30 т. Порядок тот же, что при погрузке: сверху то, что ложится на пол первым, снизу мелочь в ящики.</t>
+          <t>286 позиций, 2902 шт, 28.99 т. Порядок тот же, что при погрузке: сверху то, что ложится на пол первым, снизу мелочь в ящики.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
         <v>228</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.008353112203738489</v>
+        <v>0.007864208089005327</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>612</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.02242151170477173</v>
+        <v>0.02110919013364588</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>3108</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.1138661084614878</v>
+        <v>0.1072015734238095</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>3684</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.1349687077130377</v>
+        <v>0.1270690464907703</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ду200-250 — крупное — 7 позиций, 50 шт, 5 578 кг (20% веса). На пол, продолжение первого слоя. Ду200 встает по 3 поперек</t>
+          <t>Ду200-250 — крупное — 7 позиций, 50 шт, 5 578 кг (19% веса). На пол, продолжение первого слоя. Ду200 встает по 3 поперек</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -967,7 +967,7 @@
         <v>3934</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.1441278219715229</v>
+        <v>0.1356920816760832</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>6309</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.2311394074271321</v>
+        <v>0.2176109159365553</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>7493</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.2745169725553179</v>
+        <v>0.258449610574197</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>7823</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.2866070033765184</v>
+        <v>0.26983201701881</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>7933</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.2906370136502519</v>
+        <v>0.2736261525003476</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>9253</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.3389971369350536</v>
+        <v>0.3191557782787995</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>9262</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.3393415196311727</v>
+        <v>0.3194800044017673</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ду100-150 — среднее — 28 позиций, 124 шт, 3 694 кг (14% веса). На пол рядом с клинкетами или в низ ящиков, самое тяжелое вниз</t>
+          <t>Ду100-150 — среднее — 28 позиций, 124 шт, 4 245 кг (15% веса). На пол рядом с клинкетами или в низ ящиков, самое тяжелое вниз</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1392,16 +1392,16 @@
         <v>2</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>9400</v>
+        <v>9412</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.344375366925886</v>
+        <v>0.324653825512955</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
@@ -1449,16 +1449,16 @@
         <v>1</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>9468</v>
+        <v>9487</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.3468922905732426</v>
+        <v>0.3272407360685489</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         <v>1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>9537</v>
+        <v>9562</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.3494092142205993</v>
+        <v>0.3298276466241427</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
         <v>320</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>9857</v>
+        <v>9882</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.3611328804714603</v>
+        <v>0.3408651316613432</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
@@ -1636,10 +1636,10 @@
         <v>9</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>9866</v>
+        <v>9891</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.3614516176476556</v>
+        <v>0.3411652132857921</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         <v>5</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>9871</v>
+        <v>9896</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.3616494545156389</v>
+        <v>0.3413514708457948</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
@@ -1758,10 +1758,10 @@
         <v>135</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>10007</v>
+        <v>10032</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.3666046494952301</v>
+        <v>0.3460166403647268</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         <v>92</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>10099</v>
+        <v>10124</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.3699752035423527</v>
+        <v>0.349189917312922</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         <v>414</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>10513</v>
+        <v>10538</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.3851426967544042</v>
+        <v>0.3634696635798001</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
         <v>46</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>10559</v>
+        <v>10584</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.3868279737779654</v>
+        <v>0.3650563020538977</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         <v>109</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10668</v>
+        <v>10693</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.3908286748860718</v>
+        <v>0.3688228438228424</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         <v>90</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>10758</v>
+        <v>10783</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.3941442742476434</v>
+        <v>0.3719443825599256</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
@@ -2102,51 +2102,57 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>блины к клинкету</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
+          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>427-03-109-2</t>
+        </is>
+      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G31" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>495</v>
+        <v>130</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>11253</v>
+        <v>10914</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.412279320479444</v>
+        <v>0.3764456069266589</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr"/>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>120000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2157,12 +2163,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>блины к клинкету</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+          <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
@@ -2175,34 +2181,36 @@
         <v>1</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>11298</v>
+        <v>10956</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.4139279610459714</v>
+        <v>0.3778942768377915</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>35000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>55-650</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2214,17 +2222,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>427-03-109-2</t>
+          <t>529-03.003</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2233,37 +2241,39 @@
         </is>
       </c>
       <c r="G33" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>43.5</v>
+        <v>33.7</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>11429</v>
+        <v>10990</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.4187090186889006</v>
+        <v>0.3790566619807716</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v>120000</v>
+          <t>список менеджера, Прил. 3</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2275,12 +2285,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>блины к клинкету</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 100</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr"/>
@@ -2290,40 +2300,36 @@
         </is>
       </c>
       <c r="G34" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>42</v>
+        <v>352</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>11471</v>
+        <v>11342</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.4202477498843262</v>
+        <v>0.3911978955216922</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>55-650</t>
-        </is>
-      </c>
+          <t>Склад электрики</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2334,42 +2340,38 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>529-03.003</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>33.7</v>
+        <v>32</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>11504</v>
+        <v>11406</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.42148239848637</v>
+        <v>0.3934053925291323</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -2379,13 +2381,11 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>35000</v>
       </c>
     </row>
     <row r="36">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Задвижка клинкетная Ду100</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr"/>
@@ -2412,23 +2412,23 @@
         </is>
       </c>
       <c r="G36" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>11784</v>
+        <v>11598</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.4317406064558734</v>
+        <v>0.4000278835514525</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -2438,10 +2438,12 @@
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr"/>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>38000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2452,42 +2454,38 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>529-35-1405-01</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G37" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>26</v>
+        <v>1376</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>11810</v>
+        <v>12974</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.4326931543387559</v>
+        <v>0.4474890692114145</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -2497,13 +2495,11 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>38000</v>
       </c>
     </row>
     <row r="38">
@@ -2515,19 +2511,15 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>блины к клинкету</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>529-35.1406-01</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -2537,16 +2529,16 @@
         <v>1</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>23.6</v>
+        <v>32</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>11834</v>
+        <v>13006</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.4335577747247569</v>
+        <v>0.4485928177151345</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
@@ -2560,13 +2552,11 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>35000</v>
       </c>
     </row>
     <row r="39">
@@ -2578,42 +2568,38 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>529-03.074</t>
-        </is>
-      </c>
+          <t>Клинкет Ду 100, сталь</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G39" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>11900</v>
+        <v>13070</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.435975780888997</v>
+        <v>0.4508003147225746</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -2623,13 +2609,11 @@
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
+          <t>Фойе</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="40">
@@ -2641,12 +2625,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr"/>
@@ -2656,23 +2640,23 @@
         </is>
       </c>
       <c r="G40" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>11938</v>
+        <v>13350</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.4373791119745521</v>
+        <v>0.4604581141301251</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -2682,12 +2666,10 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>35000</v>
-      </c>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2698,38 +2680,42 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
+          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>529-35-1405-01</t>
+        </is>
+      </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G41" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>19.2</v>
+        <v>26</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>12053</v>
+        <v>13376</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.4415891052312175</v>
+        <v>0.4613549097893976</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -2739,11 +2725,13 @@
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v>38000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2755,38 +2743,42 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>529-35.1406-01</t>
+        </is>
+      </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G42" s="9" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>19.2</v>
+        <v>23.6</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>824</v>
+        <v>24</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>12877</v>
+        <v>13399</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>0.4717607235706531</v>
+        <v>0.4621689243108911</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -2796,11 +2788,13 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>38000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2812,38 +2806,42 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr"/>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>529-03.074</t>
+        </is>
+      </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>19.2</v>
+        <v>22</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>12915</v>
+        <v>13465</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0.4731640546562082</v>
+        <v>0.4644454055998137</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -2853,11 +2851,13 @@
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>Фойе</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v>30000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2897,10 +2897,10 @@
         <v>10</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>12925</v>
+        <v>13475</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>0.4735194282894374</v>
+        <v>0.4647799793650039</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         <v>16</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>12941</v>
+        <v>13491</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.4741056116019805</v>
+        <v>0.4653318536168639</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         <v>16</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>12957</v>
+        <v>13507</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>0.4746917949145236</v>
+        <v>0.465883727868724</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Ду50-80 — мелкое — 67 позиций, 531 шт, 8 985 кг (33% веса). В ящики на поддонах, нижний ярус</t>
+          <t>Ду50-80 — мелкое — 67 позиций, 531 шт, 10 078 кг (35% веса). В ящики на поддонах, нижний ярус</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -3091,10 +3091,10 @@
         <v>816</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>13773</v>
+        <v>14323</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>0.5045871438542192</v>
+        <v>0.4940293147135851</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         <v>751</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>14524</v>
+        <v>15074</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.5321157776695222</v>
+        <v>0.5199467092665614</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
@@ -3205,10 +3205,10 @@
         <v>462</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>14987</v>
+        <v>15537</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.5490564754020164</v>
+        <v>0.5358958751453161</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         <v>173</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>15160</v>
+        <v>15710</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.5554092370517018</v>
+        <v>0.5418768123498491</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
         <v>714</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>15874</v>
+        <v>16424</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.5815676673739354</v>
+        <v>0.5665042008391025</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         <v>56</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>15930</v>
+        <v>16480</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.5836193089678361</v>
+        <v>0.5684357607206126</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         <v>700</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>16630</v>
+        <v>17180</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.6092648288915947</v>
+        <v>0.5925802592394886</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -3480,51 +3480,53 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G55" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>16740</v>
+        <v>17204</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.6132948391653282</v>
+        <v>0.5934080706172786</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr"/>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>22000</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3535,38 +3537,34 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G56" s="9" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>38</v>
+        <v>1056</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>16778</v>
+        <v>18260</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>0.6146870245326179</v>
+        <v>0.6298317712400402</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
@@ -3580,13 +3578,11 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>24000</v>
       </c>
     </row>
     <row r="57">
@@ -3598,38 +3594,34 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>16797</v>
+        <v>18308</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.6153831172162628</v>
+        <v>0.6314873939956203</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
@@ -3643,10 +3635,12 @@
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O57" s="5" t="inlineStr"/>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>24000</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -3662,29 +3656,29 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная ДУ 80, сталь</t>
+          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G58" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>12</v>
+        <v>432</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>16809</v>
+        <v>18740</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>0.6158125825576081</v>
+        <v>0.6463879987958409</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
@@ -3698,11 +3692,11 @@
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O58" s="5" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="59">
@@ -3714,12 +3708,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
@@ -3729,38 +3723,36 @@
         </is>
       </c>
       <c r="G59" s="9" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>11.7</v>
+        <v>22</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>516</v>
+        <v>110</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>17325</v>
+        <v>18850</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.6347090575767965</v>
+        <v>0.6501821342773785</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v>24000</v>
-      </c>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -3771,15 +3763,19 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>527-03.055</t>
+        </is>
+      </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -3789,16 +3785,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>11.7</v>
+        <v>19</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>17348</v>
+        <v>18888</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.6355679882594869</v>
+        <v>0.6514928356255461</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
@@ -3812,11 +3808,13 @@
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>24000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3828,34 +3826,38 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr"/>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>527-03.055</t>
+        </is>
+      </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G61" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>11.7</v>
+        <v>19</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>211</v>
+        <v>19</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>17559</v>
+        <v>18907</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.6432983644037003</v>
+        <v>0.6521481862996298</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
@@ -3869,12 +3871,10 @@
       </c>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v>32000</v>
-      </c>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -3913,10 +3913,10 @@
         <v>213</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>17772</v>
+        <v>19120</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.6510946024605229</v>
+        <v>0.6594881138493681</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         <v>69</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>17841</v>
+        <v>19189</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.6536225179958648</v>
+        <v>0.6618680715605144</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
@@ -4031,16 +4031,16 @@
         <v>5</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>17941</v>
+        <v>19304</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.6572880641925384</v>
+        <v>0.6658346677457584</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
@@ -4092,16 +4092,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>17981</v>
+        <v>19350</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.6587542826712077</v>
+        <v>0.667421306219856</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
@@ -4149,16 +4149,16 @@
         <v>7</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>20</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>18042</v>
+        <v>19490</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.6609952931015051</v>
+        <v>0.6722502059236312</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
@@ -4216,10 +4216,10 @@
         <v>33</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>18075</v>
+        <v>19523</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.6621896416008115</v>
+        <v>0.6733746497117958</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
         <v>100</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>18175</v>
+        <v>19623</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.6658532873042056</v>
+        <v>0.6768238637859211</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         <v>20</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>18195</v>
+        <v>19643</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.6665860164448844</v>
+        <v>0.6775137066007461</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
@@ -4401,10 +4401,10 @@
         <v>20</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>18215</v>
+        <v>19663</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>0.6673187455855633</v>
+        <v>0.678203549415571</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Задвижка клинкетная Ду65</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr"/>
@@ -4447,19 +4447,19 @@
         </is>
       </c>
       <c r="G71" s="9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>18249</v>
+        <v>19949</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.6685643851247172</v>
+        <v>0.6880820985238656</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="N71" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O71" s="5" t="n">
-        <v>9750</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="72">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="G72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>18266</v>
+        <v>19983</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>0.6691872048942942</v>
+        <v>0.6892548313090681</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr"/>
@@ -4570,10 +4570,10 @@
         <v>17</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>18283</v>
+        <v>20000</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.6698100246638712</v>
+        <v>0.6898411977016694</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="O73" s="5" t="n">
-        <v>18000</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="74">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65</t>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr"/>
@@ -4618,19 +4618,19 @@
         </is>
       </c>
       <c r="G74" s="9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>425</v>
+        <v>17</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>18708</v>
+        <v>20017</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.685380518903296</v>
+        <v>0.6904275640942706</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
@@ -4644,11 +4644,11 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O74" s="5" t="n">
-        <v>27000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="75">
@@ -4665,33 +4665,29 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>521-03.488</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду65</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G75" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H75" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>17</v>
+        <v>425</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>18725</v>
+        <v>20442</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.686003338672873</v>
+        <v>0.7050867239093025</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
@@ -4726,12 +4722,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>522-35.4154-02</t>
+          <t>521-03.488</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -4740,19 +4736,19 @@
         </is>
       </c>
       <c r="G76" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H76" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>18827</v>
+        <v>20459</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.6897402572903349</v>
+        <v>0.7056730903019038</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
@@ -4792,7 +4788,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>522-35.4201</t>
+          <t>522-35.4154-02</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -4801,19 +4797,19 @@
         </is>
       </c>
       <c r="G77" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H77" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>18878</v>
+        <v>20561</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.691608716599066</v>
+        <v>0.7091912886575115</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
@@ -4853,7 +4849,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>521-03.195</t>
+          <t>522-35.4201</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -4862,19 +4858,19 @@
         </is>
       </c>
       <c r="G78" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H78" s="10" t="n">
         <v>17</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>19014</v>
+        <v>20612</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.6965912747556818</v>
+        <v>0.7109503878353153</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
@@ -4914,7 +4910,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>522-35.4154-02</t>
+          <t>521-03.195</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -4923,19 +4919,19 @@
         </is>
       </c>
       <c r="G79" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>19062</v>
+        <v>20748</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.698349824693311</v>
+        <v>0.7156413189761255</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
@@ -4949,13 +4945,11 @@
       </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O79" s="5" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="80">
@@ -4967,34 +4961,38 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду65</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>522-35.4154-02</t>
+        </is>
+      </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G80" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="H80" s="10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="I80" s="9" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>19180</v>
+        <v>20796</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.7027015303949342</v>
+        <v>0.7172969417317056</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
@@ -5008,11 +5006,13 @@
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="O80" s="5" t="n">
-        <v>27000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5052,10 +5052,10 @@
         <v>114</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>19294</v>
+        <v>20910</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.7068780864968035</v>
+        <v>0.7212290457762082</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
@@ -5105,16 +5105,16 @@
         <v>1</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>19301</v>
+        <v>20924</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.7071061537335336</v>
+        <v>0.7217119357465857</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
@@ -5162,16 +5162,16 @@
         <v>1</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>19307</v>
+        <v>20938</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.7073342209702638</v>
+        <v>0.7221948257169633</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         <v>205</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>19512</v>
+        <v>21143</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>0.7148446946622216</v>
+        <v>0.7292657145689198</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>71</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>19583</v>
+        <v>21214</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.7174458831116314</v>
+        <v>0.7317146565615487</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
         <v>106</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>19689</v>
+        <v>21320</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>0.7213476657857461</v>
+        <v>0.7353880695504919</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
@@ -5394,10 +5394,10 @@
         <v>60</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>19749</v>
+        <v>21380</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.7235458532077825</v>
+        <v>0.737457597994967</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr"/>
@@ -5444,39 +5444,37 @@
         </is>
       </c>
       <c r="G88" s="9" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>612</v>
+        <v>14</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>20361</v>
+        <v>21394</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>0.7459673649125542</v>
+        <v>0.7379404879653445</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O88" s="5" t="inlineStr">
-        <is>
-          <t>15-20000</t>
-        </is>
+          <t>Фойе</t>
+        </is>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="89">
@@ -5493,7 +5491,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr"/>
@@ -5503,19 +5501,19 @@
         </is>
       </c>
       <c r="G89" s="9" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H89" s="10" t="n">
         <v>12</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>36</v>
+        <v>612</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>20397</v>
+        <v>22006</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.7472862773657761</v>
+        <v>0.7590496780989904</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
@@ -5532,7 +5530,11 @@
           <t>список менеджера, Прил. 2</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>15-20000</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -5543,38 +5545,34 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>529-03.011</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый угловой Ду50</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>20409</v>
+        <v>22042</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>0.7476966056845562</v>
+        <v>0.7602913951656755</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
@@ -5588,14 +5586,10 @@
       </c>
       <c r="N90" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="O90" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -5606,17 +5600,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>527-03.054</t>
+          <t>529-03.011</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -5625,19 +5619,19 @@
         </is>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I91" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="I91" s="9" t="n">
-        <v>22</v>
-      </c>
       <c r="J91" s="9" t="n">
-        <v>20431</v>
+        <v>22054</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.748502607739303</v>
+        <v>0.7606777071419775</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
@@ -5651,12 +5645,12 @@
       </c>
       <c r="N91" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
       <c r="O91" s="5" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>по согласованию</t>
         </is>
       </c>
     </row>
@@ -5669,34 +5663,38 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Захлопка Ду50Ру6 - БРАК</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr"/>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>527-03.054</t>
+        </is>
+      </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G92" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>20463</v>
+        <v>22076</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>0.7496951244157577</v>
+        <v>0.7614365342382851</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
@@ -5710,11 +5708,13 @@
       </c>
       <c r="N92" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v>17500</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5731,33 +5731,29 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>529-35.1400-01</t>
-        </is>
-      </c>
+          <t>Захлопка Ду50Ру6 - БРАК</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G93" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>20474</v>
+        <v>22108</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.7500798072146141</v>
+        <v>0.7625592534194127</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
@@ -5771,13 +5767,11 @@
       </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O93" s="5" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>17500</v>
       </c>
     </row>
     <row r="94">
@@ -5789,19 +5783,15 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>без чертежа(527-35.1165)</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -5811,16 +5801,16 @@
         <v>1</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>20483</v>
+        <v>22119</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>0.7504241899107331</v>
+        <v>0.7629214208971958</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
@@ -5834,13 +5824,11 @@
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="O94" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="95">
@@ -5852,17 +5840,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>595-01.002</t>
+          <t>529-35.1400-01</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -5874,16 +5862,16 @@
         <v>1</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>20492</v>
+        <v>22129</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.7507649089611488</v>
+        <v>0.763283588374979</v>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
@@ -5897,11 +5885,13 @@
       </c>
       <c r="N95" s="5" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
-        </is>
-      </c>
-      <c r="O95" s="5" t="n">
-        <v>22500</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5913,17 +5903,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>595-03.011</t>
+          <t>без чертежа(527-35.1165)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -5932,19 +5922,19 @@
         </is>
       </c>
       <c r="G96" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>20520</v>
+        <v>22139</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>0.7517870661123958</v>
+        <v>0.7636078144979468</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
@@ -5958,11 +5948,13 @@
       </c>
       <c r="N96" s="5" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
-        </is>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v>25000</v>
+          <t>список менеджера, Прил. 3</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5979,12 +5971,12 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>595-03.008</t>
+          <t>595-01.002</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -6002,10 +5994,10 @@
         <v>9</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>20529</v>
+        <v>22148</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.7521277851628114</v>
+        <v>0.7639285914068404</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
@@ -6023,7 +6015,7 @@
         </is>
       </c>
       <c r="O97" s="5" t="n">
-        <v>25000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="98">
@@ -6045,7 +6037,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>595-03.011</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -6054,19 +6046,19 @@
         </is>
       </c>
       <c r="G98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>20548</v>
+        <v>22176</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>0.7528092232636426</v>
+        <v>0.7648909221335214</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
@@ -6101,10 +6093,14 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr"/>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>595-03.008</t>
+        </is>
+      </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -6120,10 +6116,10 @@
         <v>9</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>20557</v>
+        <v>22185</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.7531499423140583</v>
+        <v>0.765211699042415</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
@@ -6137,10 +6133,12 @@
       </c>
       <c r="N99" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="O99" s="5" t="inlineStr"/>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v>25000</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -6156,12 +6154,12 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -6170,19 +6168,19 @@
         </is>
       </c>
       <c r="G100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>20567</v>
+        <v>22204</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>0.753490661364474</v>
+        <v>0.7658532528602022</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
@@ -6196,10 +6194,12 @@
       </c>
       <c r="N100" s="5" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O100" s="5" t="inlineStr"/>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="O100" s="5" t="n">
+        <v>25000</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -6215,14 +6215,10 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>595-35-021</t>
-        </is>
-      </c>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
@@ -6238,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>20576</v>
+        <v>22213</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.7538313804148895</v>
+        <v>0.7661740297690959</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
@@ -6255,7 +6251,7 @@
       </c>
       <c r="N101" s="5" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr"/>
@@ -6269,34 +6265,38 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr"/>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>595-3М-48</t>
+        </is>
+      </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G102" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>20631</v>
+        <v>22222</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>0.7558463855517563</v>
+        <v>0.7664948066779894</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
@@ -6310,12 +6310,10 @@
       </c>
       <c r="N102" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v>7500</v>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -6326,34 +6324,38 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr"/>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>595-35-021</t>
+        </is>
+      </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G103" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>20704</v>
+        <v>22232</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.7585330590675785</v>
+        <v>0.7668155835868831</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
@@ -6367,12 +6369,10 @@
       </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O103" s="5" t="n">
-        <v>18000</v>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr"/>
@@ -6398,19 +6398,19 @@
         </is>
       </c>
       <c r="G104" s="9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H104" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>20878</v>
+        <v>22287</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>0.7649139086676566</v>
+        <v>0.7687126513276519</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
@@ -6424,11 +6424,11 @@
       </c>
       <c r="N104" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O104" s="5" t="n">
-        <v>22500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="105">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr"/>
@@ -6455,19 +6455,19 @@
         </is>
       </c>
       <c r="G105" s="9" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="H105" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>898</v>
+        <v>73</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>21777</v>
+        <v>22360</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.79782565923648</v>
+        <v>0.7712420749820103</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="O105" s="5" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="106">
@@ -6502,29 +6502,29 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G106" s="9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H106" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>21795</v>
+        <v>22534</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>0.7984973276154356</v>
+        <v>0.7772494561611116</v>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
@@ -6538,11 +6538,11 @@
       </c>
       <c r="N106" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="O106" s="5" t="n">
-        <v>15000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="107">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr"/>
@@ -6569,19 +6569,19 @@
         </is>
       </c>
       <c r="G107" s="9" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="H107" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>9</v>
+        <v>898</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>21804</v>
+        <v>23432</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.7988331618049134</v>
+        <v>0.8082348959270025</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="O107" s="5" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="108">
@@ -6616,37 +6616,33 @@
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>521-182.110</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr"/>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>титан</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G108" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H108" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>21850</v>
+        <v>23451</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>0.8005123327523023</v>
+        <v>0.808867251840592</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -6656,10 +6652,12 @@
       </c>
       <c r="N108" s="5" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="O108" s="5" t="inlineStr"/>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="O108" s="5" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -6670,12 +6668,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr"/>
@@ -6688,34 +6686,34 @@
         <v>1</v>
       </c>
       <c r="H109" s="10" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>21858</v>
+        <v>23460</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.8007989301133251</v>
+        <v>0.8091834297973869</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="N109" s="5" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O109" s="5" t="n">
-        <v>60000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="110">
@@ -6727,42 +6725,42 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>522-03.122-04</t>
+          <t>521-182.110</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>титан</t>
         </is>
       </c>
       <c r="G110" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H110" s="10" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>21913</v>
+        <v>23506</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>0.802813935250192</v>
+        <v>0.8107643195813609</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -6772,14 +6770,10 @@
       </c>
       <c r="N110" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O110" s="5" t="inlineStr">
-        <is>
-          <t>15-20</t>
-        </is>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="O110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -6790,34 +6784,38 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr"/>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>522-03.122-04</t>
+        </is>
+      </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G111" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H111" s="10" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>21917</v>
+        <v>23561</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.8029666440835694</v>
+        <v>0.8126613873221297</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
@@ -6831,11 +6829,13 @@
       </c>
       <c r="N111" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O111" s="5" t="n">
-        <v>25000</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>18</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>21935</v>
+        <v>23578</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>0.8036077820816634</v>
+        <v>0.8132649997851016</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
         <v>2</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>21936</v>
+        <v>23580</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.803663469496355</v>
+        <v>0.8133174278390283</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
         <v>5</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>21941</v>
+        <v>23585</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>0.8038539790729315</v>
+        <v>0.8134967869708828</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Ду40 и меньше — мелочь — 163 позиции, 2122 шт, 4 576 кг (17% веса). В ящики, верхний ярус. Ей добиваем остаток места</t>
+          <t>Ду40 и меньше — мелочь — 163 позиции, 2122 шт, 4 629 кг (16% веса). В ящики, верхний ярус. Ей добиваем остаток места</t>
         </is>
       </c>
       <c r="B115" s="4" t="n"/>
@@ -7085,10 +7085,10 @@
         <v>70</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>22011</v>
+        <v>23655</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>0.8064185310653074</v>
+        <v>0.8159112368227704</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
@@ -7136,16 +7136,16 @@
         <v>13</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>22084</v>
+        <v>23785</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.8090907142756029</v>
+        <v>0.8203952151191332</v>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
@@ -7193,16 +7193,16 @@
         <v>3</v>
       </c>
       <c r="H118" s="10" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>22101</v>
+        <v>23815</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>0.8097073719395173</v>
+        <v>0.8214299793413706</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
@@ -7254,16 +7254,16 @@
         <v>1</v>
       </c>
       <c r="H119" s="10" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>22107</v>
+        <v>23825</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.8099129244941553</v>
+        <v>0.8217749007487831</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
@@ -7315,16 +7315,16 @@
         <v>1</v>
       </c>
       <c r="H120" s="10" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>22112</v>
+        <v>23835</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>0.8101184770487934</v>
+        <v>0.8221198221561957</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
@@ -7376,16 +7376,16 @@
         <v>2</v>
       </c>
       <c r="H121" s="10" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>22124</v>
+        <v>23855</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.8105295821580696</v>
+        <v>0.8228096649710207</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         <v>11</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>22135</v>
+        <v>23866</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>0.8109399104768498</v>
+        <v>0.8231959769473227</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
@@ -7474,34 +7474,38 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr"/>
+          <t>Клапан пусковой Ду32Ру125</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>587-03.082</t>
+        </is>
+      </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H123" s="10" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>22144</v>
+        <v>23937</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.8112867575953412</v>
+        <v>0.8256242236555069</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
@@ -7515,11 +7519,13 @@
       </c>
       <c r="N123" s="5" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="O123" s="5" t="n">
-        <v>9600</v>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -7536,7 +7542,7 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr"/>
@@ -7546,19 +7552,19 @@
         </is>
       </c>
       <c r="G124" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H124" s="10" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>22201</v>
+        <v>23944</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>0.8133678403062898</v>
+        <v>0.8258656686406957</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
@@ -7576,7 +7582,7 @@
         </is>
       </c>
       <c r="O124" s="5" t="n">
-        <v>10000</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="125">
@@ -7593,33 +7599,29 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>УН522-3М38</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr">
         <is>
           <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G125" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>22220</v>
+        <v>23986</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.8140615345432728</v>
+        <v>0.8273143385518282</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
@@ -7633,11 +7635,11 @@
       </c>
       <c r="N125" s="5" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="O125" s="5" t="n">
-        <v>14000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="126">
@@ -7659,7 +7661,7 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>521-01.180</t>
+          <t>УН522-3М38</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -7668,19 +7670,19 @@
         </is>
       </c>
       <c r="G126" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H126" s="10" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>22277</v>
+        <v>24000</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>0.8161426172542214</v>
+        <v>0.8277972285222057</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
@@ -7715,33 +7717,33 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>521-01.068</t>
+          <t>521-01.180</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G127" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H127" s="10" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>22286</v>
+        <v>24042</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.8164894643727129</v>
+        <v>0.8292458984333383</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
@@ -7759,7 +7761,7 @@
         </is>
       </c>
       <c r="O127" s="5" t="n">
-        <v>9600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="128">
@@ -7771,38 +7773,38 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>клапан пусковой</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>587-03.082</t>
+          <t>521-01.068</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G128" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H128" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>22357</v>
+        <v>24049</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>0.8190686709479024</v>
+        <v>0.829487343418527</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
@@ -7816,13 +7818,11 @@
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="O128" s="5" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="n">
+        <v>9600</v>
       </c>
     </row>
     <row r="129">
@@ -7862,10 +7862,10 @@
         <v>6</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>22362</v>
+        <v>24054</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.8192811623986992</v>
+        <v>0.8296873978348263</v>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         <v>6</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>22368</v>
+        <v>24060</v>
       </c>
       <c r="K130" s="11" t="n">
-        <v>0.8194863265580892</v>
+        <v>0.8298805538229772</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
@@ -7984,10 +7984,10 @@
         <v>11</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>22379</v>
+        <v>24071</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.8198820002940557</v>
+        <v>0.8302530689429828</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
@@ -8047,10 +8047,10 @@
         <v>5</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>22384</v>
+        <v>24076</v>
       </c>
       <c r="K132" s="11" t="n">
-        <v>0.8200651825792254</v>
+        <v>0.830425529646689</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
@@ -8110,10 +8110,10 @@
         <v>8</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>22392</v>
+        <v>24084</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.8203656015269037</v>
+        <v>0.8307083652007673</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
@@ -8173,10 +8173,10 @@
         <v>4</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>22396</v>
+        <v>24088</v>
       </c>
       <c r="K134" s="11" t="n">
-        <v>0.8205158110007429</v>
+        <v>0.8308497829778064</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
         <v>3</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>22399</v>
+        <v>24091</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.8206367113089549</v>
+        <v>0.8309636070422525</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
         <v>10</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>22409</v>
+        <v>24101</v>
       </c>
       <c r="K136" s="11" t="n">
-        <v>0.8209994122335909</v>
+        <v>0.8313050792355909</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
         <v>26</v>
       </c>
       <c r="J137" s="9" t="n">
-        <v>22436</v>
+        <v>24128</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.821966614699287</v>
+        <v>0.83221567175116</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
@@ -8407,10 +8407,10 @@
         <v>63</v>
       </c>
       <c r="J138" s="9" t="n">
-        <v>22498</v>
+        <v>24190</v>
       </c>
       <c r="K138" s="11" t="n">
-        <v>0.824263720555315</v>
+        <v>0.8343783289756365</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
@@ -8468,10 +8468,10 @@
         <v>102</v>
       </c>
       <c r="J139" s="9" t="n">
-        <v>22601</v>
+        <v>24293</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.8280116301098872</v>
+        <v>0.8379068749734665</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
         <v>46</v>
       </c>
       <c r="J140" s="9" t="n">
-        <v>22647</v>
+        <v>24339</v>
       </c>
       <c r="K140" s="11" t="n">
-        <v>0.8297042344248553</v>
+        <v>0.8395004118757123</v>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
@@ -8594,10 +8594,10 @@
         <v>3</v>
       </c>
       <c r="J141" s="9" t="n">
-        <v>22650</v>
+        <v>24342</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.8298251347330673</v>
+        <v>0.8396142359401585</v>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
@@ -8657,10 +8657,10 @@
         <v>3</v>
       </c>
       <c r="J142" s="9" t="n">
-        <v>22654</v>
+        <v>24345</v>
       </c>
       <c r="K142" s="11" t="n">
-        <v>0.8299460350412793</v>
+        <v>0.8397280600046045</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
@@ -8720,10 +8720,10 @@
         <v>46</v>
       </c>
       <c r="J143" s="9" t="n">
-        <v>22700</v>
+        <v>24392</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.8316386393562474</v>
+        <v>0.8413215969068504</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
@@ -8781,10 +8781,10 @@
         <v>3</v>
       </c>
       <c r="J144" s="9" t="n">
-        <v>22703</v>
+        <v>24395</v>
       </c>
       <c r="K144" s="11" t="n">
-        <v>0.8317595396644594</v>
+        <v>0.8414354209712965</v>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
         <v>3</v>
       </c>
       <c r="J145" s="9" t="n">
-        <v>22706</v>
+        <v>24398</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.8318804399726712</v>
+        <v>0.8415492450357426</v>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
@@ -8903,10 +8903,10 @@
         <v>102</v>
       </c>
       <c r="J146" s="9" t="n">
-        <v>22809</v>
+        <v>24501</v>
       </c>
       <c r="K146" s="11" t="n">
-        <v>0.8356283495272434</v>
+        <v>0.8450777910335726</v>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
@@ -8964,10 +8964,10 @@
         <v>4</v>
       </c>
       <c r="J147" s="9" t="n">
-        <v>22813</v>
+        <v>24505</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.8357932135838961</v>
+        <v>0.8452330056669082</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
@@ -9023,10 +9023,10 @@
         <v>6</v>
       </c>
       <c r="J148" s="9" t="n">
-        <v>22819</v>
+        <v>24511</v>
       </c>
       <c r="K148" s="11" t="n">
-        <v>0.8359947140975829</v>
+        <v>0.8454227124409851</v>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
@@ -9086,10 +9086,10 @@
         <v>341</v>
       </c>
       <c r="J149" s="9" t="n">
-        <v>23160</v>
+        <v>24852</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.8484877459461566</v>
+        <v>0.8571845324337518</v>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
         <v>6</v>
       </c>
       <c r="J150" s="9" t="n">
-        <v>23165</v>
+        <v>24857</v>
       </c>
       <c r="K150" s="11" t="n">
-        <v>0.8486892464598432</v>
+        <v>0.8573742392078287</v>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
         <v>72</v>
       </c>
       <c r="J151" s="9" t="n">
-        <v>23237</v>
+        <v>24929</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>0.85130875313777</v>
+        <v>0.8598404272708282</v>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
         <v>6</v>
       </c>
       <c r="J152" s="9" t="n">
-        <v>23242</v>
+        <v>24934</v>
       </c>
       <c r="K152" s="11" t="n">
-        <v>0.8515102536514567</v>
+        <v>0.8600301340449051</v>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
@@ -9332,10 +9332,10 @@
         <v>6</v>
       </c>
       <c r="J153" s="9" t="n">
-        <v>23248</v>
+        <v>24940</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>0.8517117541651434</v>
+        <v>0.860219840818982</v>
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
@@ -9393,10 +9393,10 @@
         <v>3</v>
       </c>
       <c r="J154" s="9" t="n">
-        <v>23251</v>
+        <v>24942</v>
       </c>
       <c r="K154" s="11" t="n">
-        <v>0.8518179998905419</v>
+        <v>0.8603198680271317</v>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>5</v>
       </c>
       <c r="J155" s="9" t="n">
-        <v>23256</v>
+        <v>24947</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.8520011821757115</v>
+        <v>0.8604923287308379</v>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
@@ -9519,10 +9519,10 @@
         <v>4</v>
       </c>
       <c r="J156" s="9" t="n">
-        <v>23259</v>
+        <v>24951</v>
       </c>
       <c r="K156" s="11" t="n">
-        <v>0.8521294097753304</v>
+        <v>0.8606130512234322</v>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
@@ -9576,10 +9576,10 @@
         <v>138</v>
       </c>
       <c r="J157" s="9" t="n">
-        <v>23397</v>
+        <v>25089</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>0.8571943999602727</v>
+        <v>0.8653815896809103</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         <v>2</v>
       </c>
       <c r="J158" s="9" t="n">
-        <v>23399</v>
+        <v>25091</v>
       </c>
       <c r="K158" s="11" t="n">
-        <v>0.8572585137600821</v>
+        <v>0.8654419509272074</v>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
@@ -9698,10 +9698,10 @@
         <v>2</v>
       </c>
       <c r="J159" s="9" t="n">
-        <v>23401</v>
+        <v>25093</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.8573226275598914</v>
+        <v>0.8655023121735047</v>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
@@ -9755,10 +9755,10 @@
         <v>10</v>
       </c>
       <c r="J160" s="9" t="n">
-        <v>23411</v>
+        <v>25103</v>
       </c>
       <c r="K160" s="11" t="n">
-        <v>0.8577073103587478</v>
+        <v>0.8658644796512878</v>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         <v>14</v>
       </c>
       <c r="J161" s="9" t="n">
-        <v>23425</v>
+        <v>25117</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>0.858220220757223</v>
+        <v>0.8663473696216654</v>
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
@@ -9877,10 +9877,10 @@
         <v>13</v>
       </c>
       <c r="J162" s="9" t="n">
-        <v>23438</v>
+        <v>25130</v>
       </c>
       <c r="K162" s="11" t="n">
-        <v>0.8586891674072574</v>
+        <v>0.8667888690231533</v>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
@@ -9940,10 +9940,10 @@
         <v>1</v>
       </c>
       <c r="J163" s="9" t="n">
-        <v>23439</v>
+        <v>25131</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.8587331311556982</v>
+        <v>0.8668302595920429</v>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
         <v>243</v>
       </c>
       <c r="J164" s="9" t="n">
-        <v>23682</v>
+        <v>25374</v>
       </c>
       <c r="K164" s="11" t="n">
-        <v>0.8676357902149457</v>
+        <v>0.8752118497921669</v>
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
@@ -10066,10 +10066,10 @@
         <v>12</v>
       </c>
       <c r="J165" s="9" t="n">
-        <v>23694</v>
+        <v>25386</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.8680607731165394</v>
+        <v>0.8756119586247654</v>
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
@@ -10129,10 +10129,10 @@
         <v>39</v>
       </c>
       <c r="J166" s="9" t="n">
-        <v>23733</v>
+        <v>25425</v>
       </c>
       <c r="K166" s="11" t="n">
-        <v>0.8694969222322699</v>
+        <v>0.8769640505418225</v>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
@@ -10186,16 +10186,16 @@
         <v>8</v>
       </c>
       <c r="H167" s="10" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J167" s="9" t="n">
-        <v>23760</v>
+        <v>25457</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.8704835744945328</v>
+        <v>0.8780677990455426</v>
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
@@ -10253,10 +10253,10 @@
         <v>20</v>
       </c>
       <c r="J168" s="9" t="n">
-        <v>23780</v>
+        <v>25477</v>
       </c>
       <c r="K168" s="11" t="n">
-        <v>0.8712016490523981</v>
+        <v>0.878743845004071</v>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
@@ -10316,10 +10316,10 @@
         <v>7</v>
       </c>
       <c r="J169" s="9" t="n">
-        <v>23787</v>
+        <v>25484</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>0.8714654315430423</v>
+        <v>0.8789921884174081</v>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
@@ -10379,10 +10379,10 @@
         <v>2</v>
       </c>
       <c r="J170" s="9" t="n">
-        <v>23789</v>
+        <v>25486</v>
       </c>
       <c r="K170" s="11" t="n">
-        <v>0.8715496953942204</v>
+        <v>0.8790715203411129</v>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
@@ -10438,10 +10438,10 @@
         <v>2</v>
       </c>
       <c r="J171" s="9" t="n">
-        <v>23791</v>
+        <v>25488</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.8716211364854366</v>
+        <v>0.8791387800155583</v>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
@@ -10499,10 +10499,10 @@
         <v>4</v>
       </c>
       <c r="J172" s="9" t="n">
-        <v>23795</v>
+        <v>25492</v>
       </c>
       <c r="K172" s="11" t="n">
-        <v>0.8717640186678691</v>
+        <v>0.8792732993644493</v>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         <v>2</v>
       </c>
       <c r="J173" s="9" t="n">
-        <v>23797</v>
+        <v>25494</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>0.8718354597590853</v>
+        <v>0.8793405590388947</v>
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
@@ -10621,10 +10621,10 @@
         <v>2</v>
       </c>
       <c r="J174" s="9" t="n">
-        <v>23799</v>
+        <v>25496</v>
       </c>
       <c r="K174" s="11" t="n">
-        <v>0.8719069008503015</v>
+        <v>0.8794078187133403</v>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
@@ -10678,10 +10678,10 @@
         <v>195</v>
       </c>
       <c r="J175" s="9" t="n">
-        <v>23994</v>
+        <v>25691</v>
       </c>
       <c r="K175" s="11" t="n">
-        <v>0.87905100997192</v>
+        <v>0.8861337861578843</v>
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
@@ -10739,10 +10739,10 @@
         <v>8</v>
       </c>
       <c r="J176" s="9" t="n">
-        <v>24002</v>
+        <v>25699</v>
       </c>
       <c r="K176" s="11" t="n">
-        <v>0.8793367743367847</v>
+        <v>0.886402824855666</v>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>2</v>
       </c>
       <c r="J177" s="9" t="n">
-        <v>24004</v>
+        <v>25701</v>
       </c>
       <c r="K177" s="11" t="n">
-        <v>0.8794082154280009</v>
+        <v>0.8864700845301114</v>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         <v>2</v>
       </c>
       <c r="J178" s="9" t="n">
-        <v>24006</v>
+        <v>25703</v>
       </c>
       <c r="K178" s="11" t="n">
-        <v>0.8794796565192171</v>
+        <v>0.886537344204557</v>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
@@ -10922,10 +10922,10 @@
         <v>25</v>
       </c>
       <c r="J179" s="9" t="n">
-        <v>24031</v>
+        <v>25728</v>
       </c>
       <c r="K179" s="11" t="n">
-        <v>0.8804083907050274</v>
+        <v>0.8874117199723476</v>
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
@@ -10983,10 +10983,10 @@
         <v>2</v>
       </c>
       <c r="J180" s="9" t="n">
-        <v>24033</v>
+        <v>25730</v>
       </c>
       <c r="K180" s="11" t="n">
-        <v>0.8804798317962437</v>
+        <v>0.8874789796467931</v>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
@@ -11044,10 +11044,10 @@
         <v>4</v>
       </c>
       <c r="J181" s="9" t="n">
-        <v>24037</v>
+        <v>25734</v>
       </c>
       <c r="K181" s="11" t="n">
-        <v>0.8806227139786761</v>
+        <v>0.887613498995684</v>
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
@@ -11105,10 +11105,10 @@
         <v>4</v>
       </c>
       <c r="J182" s="9" t="n">
-        <v>24041</v>
+        <v>25738</v>
       </c>
       <c r="K182" s="11" t="n">
-        <v>0.8807655961611085</v>
+        <v>0.887748018344575</v>
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
@@ -11166,10 +11166,10 @@
         <v>41</v>
       </c>
       <c r="J183" s="9" t="n">
-        <v>24082</v>
+        <v>25779</v>
       </c>
       <c r="K183" s="11" t="n">
-        <v>0.8822658590766483</v>
+        <v>0.8891604715079292</v>
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
@@ -11227,10 +11227,10 @@
         <v>31</v>
       </c>
       <c r="J184" s="9" t="n">
-        <v>24113</v>
+        <v>25810</v>
       </c>
       <c r="K184" s="11" t="n">
-        <v>0.8834089165361073</v>
+        <v>0.8902366262990563</v>
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
@@ -11288,10 +11288,10 @@
         <v>4</v>
       </c>
       <c r="J185" s="9" t="n">
-        <v>24117</v>
+        <v>25814</v>
       </c>
       <c r="K185" s="11" t="n">
-        <v>0.8835517987185397</v>
+        <v>0.8903711456479472</v>
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
@@ -11349,10 +11349,10 @@
         <v>2</v>
       </c>
       <c r="J186" s="9" t="n">
-        <v>24119</v>
+        <v>25816</v>
       </c>
       <c r="K186" s="11" t="n">
-        <v>0.883623239809756</v>
+        <v>0.8904384053223927</v>
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
@@ -11410,10 +11410,10 @@
         <v>2</v>
       </c>
       <c r="J187" s="9" t="n">
-        <v>24121</v>
+        <v>25818</v>
       </c>
       <c r="K187" s="11" t="n">
-        <v>0.8836946809009721</v>
+        <v>0.8905056649968381</v>
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
@@ -11471,10 +11471,10 @@
         <v>6</v>
       </c>
       <c r="J188" s="9" t="n">
-        <v>24126</v>
+        <v>25823</v>
       </c>
       <c r="K188" s="11" t="n">
-        <v>0.8839090041746207</v>
+        <v>0.8907074440201744</v>
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
@@ -11532,10 +11532,10 @@
         <v>199</v>
       </c>
       <c r="J189" s="9" t="n">
-        <v>24325</v>
+        <v>26022</v>
       </c>
       <c r="K189" s="11" t="n">
-        <v>0.8911959954786716</v>
+        <v>0.8975679308136094</v>
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
@@ -11593,10 +11593,10 @@
         <v>14</v>
       </c>
       <c r="J190" s="9" t="n">
-        <v>24339</v>
+        <v>26036</v>
       </c>
       <c r="K190" s="11" t="n">
-        <v>0.891696083117185</v>
+        <v>0.8980387485347275</v>
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
@@ -11654,10 +11654,10 @@
         <v>18</v>
       </c>
       <c r="J191" s="9" t="n">
-        <v>24357</v>
+        <v>26054</v>
       </c>
       <c r="K191" s="11" t="n">
-        <v>0.8923390529381305</v>
+        <v>0.8986440856047364</v>
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         <v>8</v>
       </c>
       <c r="J192" s="9" t="n">
-        <v>24364</v>
+        <v>26061</v>
       </c>
       <c r="K192" s="11" t="n">
-        <v>0.8926248173029953</v>
+        <v>0.8989131243025181</v>
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
@@ -11776,10 +11776,10 @@
         <v>21</v>
       </c>
       <c r="J193" s="9" t="n">
-        <v>24386</v>
+        <v>26083</v>
       </c>
       <c r="K193" s="11" t="n">
-        <v>0.8934106693063733</v>
+        <v>0.8996529807214181</v>
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
@@ -11837,10 +11837,10 @@
         <v>21</v>
       </c>
       <c r="J194" s="9" t="n">
-        <v>24407</v>
+        <v>26104</v>
       </c>
       <c r="K194" s="11" t="n">
-        <v>0.8941965213097514</v>
+        <v>0.9003928371403179</v>
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
@@ -11898,10 +11898,10 @@
         <v>4</v>
       </c>
       <c r="J195" s="9" t="n">
-        <v>24411</v>
+        <v>26108</v>
       </c>
       <c r="K195" s="11" t="n">
-        <v>0.8943394034921838</v>
+        <v>0.9005273564892089</v>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         <v>2</v>
       </c>
       <c r="J196" s="9" t="n">
-        <v>24413</v>
+        <v>26110</v>
       </c>
       <c r="K196" s="11" t="n">
-        <v>0.8944108445834</v>
+        <v>0.9005946161636543</v>
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
@@ -12020,10 +12020,10 @@
         <v>6</v>
       </c>
       <c r="J197" s="9" t="n">
-        <v>24419</v>
+        <v>26116</v>
       </c>
       <c r="K197" s="11" t="n">
-        <v>0.8946251678570485</v>
+        <v>0.9007963951869906</v>
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>140</v>
       </c>
       <c r="J198" s="9" t="n">
-        <v>24559</v>
+        <v>26256</v>
       </c>
       <c r="K198" s="11" t="n">
-        <v>0.8997689264246138</v>
+        <v>0.9056390917470624</v>
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
@@ -12142,10 +12142,10 @@
         <v>45</v>
       </c>
       <c r="J199" s="9" t="n">
-        <v>24604</v>
+        <v>26301</v>
       </c>
       <c r="K199" s="11" t="n">
-        <v>0.9014120715225861</v>
+        <v>0.9071860642593074</v>
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
@@ -12203,10 +12203,10 @@
         <v>2</v>
       </c>
       <c r="J200" s="9" t="n">
-        <v>24606</v>
+        <v>26303</v>
       </c>
       <c r="K200" s="11" t="n">
-        <v>0.9014835126138022</v>
+        <v>0.9072533239337529</v>
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>10</v>
       </c>
       <c r="J201" s="9" t="n">
-        <v>24616</v>
+        <v>26313</v>
       </c>
       <c r="K201" s="11" t="n">
-        <v>0.9018407180698832</v>
+        <v>0.9075896223059801</v>
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
@@ -12325,10 +12325,10 @@
         <v>10</v>
       </c>
       <c r="J202" s="9" t="n">
-        <v>24626</v>
+        <v>26323</v>
       </c>
       <c r="K202" s="11" t="n">
-        <v>0.9021979235259641</v>
+        <v>0.9079259206782073</v>
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
@@ -12386,10 +12386,10 @@
         <v>2</v>
       </c>
       <c r="J203" s="9" t="n">
-        <v>24628</v>
+        <v>26325</v>
       </c>
       <c r="K203" s="11" t="n">
-        <v>0.9022693646171803</v>
+        <v>0.9079931803526528</v>
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
@@ -12447,10 +12447,10 @@
         <v>2</v>
       </c>
       <c r="J204" s="9" t="n">
-        <v>24630</v>
+        <v>26327</v>
       </c>
       <c r="K204" s="11" t="n">
-        <v>0.9023408057083965</v>
+        <v>0.9080604400270982</v>
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
@@ -12508,10 +12508,10 @@
         <v>4</v>
       </c>
       <c r="J205" s="9" t="n">
-        <v>24633</v>
+        <v>26330</v>
       </c>
       <c r="K205" s="11" t="n">
-        <v>0.9024836878908289</v>
+        <v>0.9081949593759892</v>
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
@@ -12569,10 +12569,10 @@
         <v>64</v>
       </c>
       <c r="J206" s="9" t="n">
-        <v>24697</v>
+        <v>26394</v>
       </c>
       <c r="K206" s="11" t="n">
-        <v>0.9048210938495943</v>
+        <v>0.9103955579552809</v>
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         <v>4</v>
       </c>
       <c r="J207" s="9" t="n">
-        <v>24701</v>
+        <v>26398</v>
       </c>
       <c r="K207" s="11" t="n">
-        <v>0.9049529850949164</v>
+        <v>0.9105197296619494</v>
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
@@ -12693,10 +12693,10 @@
         <v>2</v>
       </c>
       <c r="J208" s="9" t="n">
-        <v>24703</v>
+        <v>26400</v>
       </c>
       <c r="K208" s="11" t="n">
-        <v>0.9050189307175776</v>
+        <v>0.9105818155152836</v>
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
@@ -12756,10 +12756,10 @@
         <v>5</v>
       </c>
       <c r="J209" s="9" t="n">
-        <v>24708</v>
+        <v>26405</v>
       </c>
       <c r="K209" s="11" t="n">
-        <v>0.9052057766484506</v>
+        <v>0.910757725433064</v>
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
@@ -12815,10 +12815,10 @@
         <v>2</v>
       </c>
       <c r="J210" s="9" t="n">
-        <v>24709</v>
+        <v>26406</v>
       </c>
       <c r="K210" s="11" t="n">
-        <v>0.9052607313340014</v>
+        <v>0.9108094636441758</v>
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
@@ -12876,10 +12876,10 @@
         <v>39</v>
       </c>
       <c r="J211" s="9" t="n">
-        <v>24748</v>
+        <v>26445</v>
       </c>
       <c r="K211" s="11" t="n">
-        <v>0.9066895531583251</v>
+        <v>0.9121546571330846</v>
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
@@ -12939,10 +12939,10 @@
         <v>7</v>
       </c>
       <c r="J212" s="9" t="n">
-        <v>24755</v>
+        <v>26452</v>
       </c>
       <c r="K212" s="11" t="n">
-        <v>0.9069533356489695</v>
+        <v>0.9124030005464216</v>
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
@@ -13002,10 +13002,10 @@
         <v>17</v>
       </c>
       <c r="J213" s="9" t="n">
-        <v>24773</v>
+        <v>26470</v>
       </c>
       <c r="K213" s="11" t="n">
-        <v>0.9075798190642499</v>
+        <v>0.912992816153097</v>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
@@ -13065,10 +13065,10 @@
         <v>17</v>
       </c>
       <c r="J214" s="9" t="n">
-        <v>24790</v>
+        <v>26487</v>
       </c>
       <c r="K214" s="11" t="n">
-        <v>0.9082099661252336</v>
+        <v>0.9135860809738466</v>
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
@@ -13128,10 +13128,10 @@
         <v>3</v>
       </c>
       <c r="J215" s="9" t="n">
-        <v>24792</v>
+        <v>26489</v>
       </c>
       <c r="K215" s="11" t="n">
-        <v>0.9083052209135218</v>
+        <v>0.9136757605397738</v>
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
@@ -13187,10 +13187,10 @@
         <v>3</v>
       </c>
       <c r="J216" s="9" t="n">
-        <v>24795</v>
+        <v>26492</v>
       </c>
       <c r="K216" s="11" t="n">
-        <v>0.90840047570181</v>
+        <v>0.913765440105701</v>
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
@@ -13248,10 +13248,10 @@
         <v>3</v>
       </c>
       <c r="J217" s="9" t="n">
-        <v>24798</v>
+        <v>26495</v>
       </c>
       <c r="K217" s="11" t="n">
-        <v>0.9084957304900982</v>
+        <v>0.9138551196716282</v>
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
@@ -13309,10 +13309,10 @@
         <v>5</v>
       </c>
       <c r="J218" s="9" t="n">
-        <v>24803</v>
+        <v>26500</v>
       </c>
       <c r="K218" s="11" t="n">
-        <v>0.9086862400666748</v>
+        <v>0.9140344788034828</v>
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
@@ -13370,10 +13370,10 @@
         <v>3</v>
       </c>
       <c r="J219" s="9" t="n">
-        <v>24805</v>
+        <v>26502</v>
       </c>
       <c r="K219" s="11" t="n">
-        <v>0.908781494854963</v>
+        <v>0.91412415836941</v>
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
@@ -13431,10 +13431,10 @@
         <v>5</v>
       </c>
       <c r="J220" s="9" t="n">
-        <v>24811</v>
+        <v>26508</v>
       </c>
       <c r="K220" s="11" t="n">
-        <v>0.9089720044315395</v>
+        <v>0.9143035175012645</v>
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
@@ -13492,10 +13492,10 @@
         <v>3</v>
       </c>
       <c r="J221" s="9" t="n">
-        <v>24813</v>
+        <v>26510</v>
       </c>
       <c r="K221" s="11" t="n">
-        <v>0.9090672592198277</v>
+        <v>0.9143931970671917</v>
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
@@ -13553,10 +13553,10 @@
         <v>3</v>
       </c>
       <c r="J222" s="9" t="n">
-        <v>24816</v>
+        <v>26513</v>
       </c>
       <c r="K222" s="11" t="n">
-        <v>0.9091625140081159</v>
+        <v>0.9144828766331189</v>
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
@@ -13614,10 +13614,10 @@
         <v>3</v>
       </c>
       <c r="J223" s="9" t="n">
-        <v>24818</v>
+        <v>26515</v>
       </c>
       <c r="K223" s="11" t="n">
-        <v>0.9092577687964041</v>
+        <v>0.9145725561990461</v>
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
@@ -13675,10 +13675,10 @@
         <v>8</v>
       </c>
       <c r="J224" s="9" t="n">
-        <v>24826</v>
+        <v>26523</v>
       </c>
       <c r="K224" s="11" t="n">
-        <v>0.9095435331612688</v>
+        <v>0.9148415948968278</v>
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
@@ -13730,10 +13730,10 @@
         <v>26</v>
       </c>
       <c r="J225" s="9" t="n">
-        <v>24852</v>
+        <v>26549</v>
       </c>
       <c r="K225" s="11" t="n">
-        <v>0.9104960810441513</v>
+        <v>0.9157383905561004</v>
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
@@ -13791,10 +13791,10 @@
         <v>39</v>
       </c>
       <c r="J226" s="9" t="n">
-        <v>24891</v>
+        <v>26588</v>
       </c>
       <c r="K226" s="11" t="n">
-        <v>0.9119249028684749</v>
+        <v>0.9170835840450091</v>
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
@@ -13852,10 +13852,10 @@
         <v>5</v>
       </c>
       <c r="J227" s="9" t="n">
-        <v>24896</v>
+        <v>26593</v>
       </c>
       <c r="K227" s="11" t="n">
-        <v>0.9121154124450515</v>
+        <v>0.9172629431768637</v>
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
@@ -13913,10 +13913,10 @@
         <v>3</v>
       </c>
       <c r="J228" s="9" t="n">
-        <v>24899</v>
+        <v>26596</v>
       </c>
       <c r="K228" s="11" t="n">
-        <v>0.9122106672333397</v>
+        <v>0.9173526227427909</v>
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
@@ -13974,10 +13974,10 @@
         <v>3</v>
       </c>
       <c r="J229" s="9" t="n">
-        <v>24902</v>
+        <v>26599</v>
       </c>
       <c r="K229" s="11" t="n">
-        <v>0.9123059220216279</v>
+        <v>0.9174423023087181</v>
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
@@ -14035,10 +14035,10 @@
         <v>10</v>
       </c>
       <c r="J230" s="9" t="n">
-        <v>24912</v>
+        <v>26609</v>
       </c>
       <c r="K230" s="11" t="n">
-        <v>0.9126869411747809</v>
+        <v>0.9178010205724272</v>
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
@@ -14096,10 +14096,10 @@
         <v>8</v>
       </c>
       <c r="J231" s="9" t="n">
-        <v>24920</v>
+        <v>26617</v>
       </c>
       <c r="K231" s="11" t="n">
-        <v>0.9129727055396456</v>
+        <v>0.9180700592702089</v>
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
@@ -14157,10 +14157,10 @@
         <v>16</v>
       </c>
       <c r="J232" s="9" t="n">
-        <v>24935</v>
+        <v>26632</v>
       </c>
       <c r="K232" s="11" t="n">
-        <v>0.913544234269375</v>
+        <v>0.9186081366657723</v>
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
@@ -14218,10 +14218,10 @@
         <v>18</v>
       </c>
       <c r="J233" s="9" t="n">
-        <v>24954</v>
+        <v>26651</v>
       </c>
       <c r="K233" s="11" t="n">
-        <v>0.9142110177873928</v>
+        <v>0.9192358936272632</v>
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
@@ -14279,10 +14279,10 @@
         <v>5</v>
       </c>
       <c r="J234" s="9" t="n">
-        <v>24959</v>
+        <v>26656</v>
       </c>
       <c r="K234" s="11" t="n">
-        <v>0.9144015273639693</v>
+        <v>0.9194152527591177</v>
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
@@ -14336,10 +14336,10 @@
         <v>114</v>
       </c>
       <c r="J235" s="9" t="n">
-        <v>25073</v>
+        <v>26770</v>
       </c>
       <c r="K235" s="11" t="n">
-        <v>0.9185927380486522</v>
+        <v>0.9233611536599169</v>
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         <v>1</v>
       </c>
       <c r="J236" s="9" t="n">
-        <v>25074</v>
+        <v>26771</v>
       </c>
       <c r="K236" s="11" t="n">
-        <v>0.9186403654427963</v>
+        <v>0.9234059934428805</v>
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
@@ -14456,10 +14456,10 @@
         <v>4</v>
       </c>
       <c r="J237" s="9" t="n">
-        <v>25079</v>
+        <v>26775</v>
       </c>
       <c r="K237" s="11" t="n">
-        <v>0.918790823336512</v>
+        <v>0.9235439620058455</v>
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
@@ -14517,10 +14517,10 @@
         <v>1</v>
       </c>
       <c r="J238" s="9" t="n">
-        <v>25079</v>
+        <v>26776</v>
       </c>
       <c r="K238" s="11" t="n">
-        <v>0.9188237961478426</v>
+        <v>0.9235750049325127</v>
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
@@ -14580,10 +14580,10 @@
         <v>1</v>
       </c>
       <c r="J239" s="9" t="n">
-        <v>25080</v>
+        <v>26777</v>
       </c>
       <c r="K239" s="11" t="n">
-        <v>0.9188531053134696</v>
+        <v>0.9236025986451056</v>
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
@@ -14643,10 +14643,10 @@
         <v>8</v>
       </c>
       <c r="J240" s="9" t="n">
-        <v>25088</v>
+        <v>26785</v>
       </c>
       <c r="K240" s="11" t="n">
-        <v>0.9191278787412243</v>
+        <v>0.9238612897006651</v>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
@@ -14706,10 +14706,10 @@
         <v>8</v>
       </c>
       <c r="J241" s="9" t="n">
-        <v>25095</v>
+        <v>26792</v>
       </c>
       <c r="K241" s="11" t="n">
-        <v>0.9194026521689788</v>
+        <v>0.9241199807562245</v>
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
@@ -14769,10 +14769,10 @@
         <v>4</v>
       </c>
       <c r="J242" s="9" t="n">
-        <v>25099</v>
+        <v>26796</v>
       </c>
       <c r="K242" s="11" t="n">
-        <v>0.9195418707057078</v>
+        <v>0.9242510508910412</v>
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>14</v>
       </c>
       <c r="J243" s="9" t="n">
-        <v>25113</v>
+        <v>26810</v>
       </c>
       <c r="K243" s="11" t="n">
-        <v>0.9200536087375578</v>
+        <v>0.924732837112915</v>
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
@@ -14889,10 +14889,10 @@
         <v>193</v>
       </c>
       <c r="J244" s="9" t="n">
-        <v>25306</v>
+        <v>27003</v>
       </c>
       <c r="K244" s="11" t="n">
-        <v>0.9271326515114839</v>
+        <v>0.9313975465155026</v>
       </c>
       <c r="L244" s="5" t="inlineStr">
         <is>
@@ -14950,10 +14950,10 @@
         <v>9</v>
       </c>
       <c r="J245" s="9" t="n">
-        <v>25316</v>
+        <v>27012</v>
       </c>
       <c r="K245" s="11" t="n">
-        <v>0.9274738101993841</v>
+        <v>0.9317187373300851</v>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
@@ -15011,10 +15011,10 @@
         <v>2</v>
       </c>
       <c r="J246" s="9" t="n">
-        <v>25318</v>
+        <v>27015</v>
       </c>
       <c r="K246" s="11" t="n">
-        <v>0.9275590998713592</v>
+        <v>0.9317990350337308</v>
       </c>
       <c r="L246" s="5" t="inlineStr">
         <is>
@@ -15072,10 +15072,10 @@
         <v>16</v>
       </c>
       <c r="J247" s="9" t="n">
-        <v>25334</v>
+        <v>27031</v>
       </c>
       <c r="K247" s="11" t="n">
-        <v>0.9281561275751842</v>
+        <v>0.9323611189592502</v>
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
@@ -15133,10 +15133,10 @@
         <v>5</v>
       </c>
       <c r="J248" s="9" t="n">
-        <v>25339</v>
+        <v>27036</v>
       </c>
       <c r="K248" s="11" t="n">
-        <v>0.9283267069191342</v>
+        <v>0.9325217143665414</v>
       </c>
       <c r="L248" s="5" t="inlineStr">
         <is>
@@ -15194,10 +15194,10 @@
         <v>12</v>
       </c>
       <c r="J249" s="9" t="n">
-        <v>25351</v>
+        <v>27047</v>
       </c>
       <c r="K249" s="11" t="n">
-        <v>0.9287531552790093</v>
+        <v>0.9329232028847696</v>
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
@@ -15255,10 +15255,10 @@
         <v>2</v>
       </c>
       <c r="J250" s="9" t="n">
-        <v>25353</v>
+        <v>27050</v>
       </c>
       <c r="K250" s="11" t="n">
-        <v>0.9288384449509843</v>
+        <v>0.9330035005884152</v>
       </c>
       <c r="L250" s="5" t="inlineStr">
         <is>
@@ -15316,10 +15316,10 @@
         <v>2</v>
       </c>
       <c r="J251" s="9" t="n">
-        <v>25355</v>
+        <v>27052</v>
       </c>
       <c r="K251" s="11" t="n">
-        <v>0.9289237346229594</v>
+        <v>0.9330837982920609</v>
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
@@ -15377,10 +15377,10 @@
         <v>42</v>
       </c>
       <c r="J252" s="9" t="n">
-        <v>25397</v>
+        <v>27094</v>
       </c>
       <c r="K252" s="11" t="n">
-        <v>0.9304589487185095</v>
+        <v>0.9345291569576822</v>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
@@ -15438,10 +15438,10 @@
         <v>2</v>
       </c>
       <c r="J253" s="9" t="n">
-        <v>25399</v>
+        <v>27096</v>
       </c>
       <c r="K253" s="11" t="n">
-        <v>0.9305442383904846</v>
+        <v>0.9346094546613279</v>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
@@ -15499,10 +15499,10 @@
         <v>5</v>
       </c>
       <c r="J254" s="9" t="n">
-        <v>25404</v>
+        <v>27101</v>
       </c>
       <c r="K254" s="11" t="n">
-        <v>0.9307148177344347</v>
+        <v>0.9347700500686191</v>
       </c>
       <c r="L254" s="5" t="inlineStr">
         <is>
@@ -15560,10 +15560,10 @@
         <v>2</v>
       </c>
       <c r="J255" s="9" t="n">
-        <v>25406</v>
+        <v>27103</v>
       </c>
       <c r="K255" s="11" t="n">
-        <v>0.9308001074064097</v>
+        <v>0.9348503477722648</v>
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>2</v>
       </c>
       <c r="J256" s="9" t="n">
-        <v>25409</v>
+        <v>27106</v>
       </c>
       <c r="K256" s="11" t="n">
-        <v>0.9308853970783848</v>
+        <v>0.9349306454759105</v>
       </c>
       <c r="L256" s="5" t="inlineStr">
         <is>
@@ -15682,10 +15682,10 @@
         <v>12</v>
       </c>
       <c r="J257" s="9" t="n">
-        <v>25420</v>
+        <v>27117</v>
       </c>
       <c r="K257" s="11" t="n">
-        <v>0.9313118454382598</v>
+        <v>0.9353321339941387</v>
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
@@ -15743,10 +15743,10 @@
         <v>2</v>
       </c>
       <c r="J258" s="9" t="n">
-        <v>25423</v>
+        <v>27120</v>
       </c>
       <c r="K258" s="11" t="n">
-        <v>0.9313971351102348</v>
+        <v>0.9354124316977843</v>
       </c>
       <c r="L258" s="5" t="inlineStr">
         <is>
@@ -15804,10 +15804,10 @@
         <v>14</v>
       </c>
       <c r="J259" s="9" t="n">
-        <v>25437</v>
+        <v>27134</v>
       </c>
       <c r="K259" s="11" t="n">
-        <v>0.9319088731420849</v>
+        <v>0.9358942179196582</v>
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
@@ -15865,10 +15865,10 @@
         <v>2</v>
       </c>
       <c r="J260" s="9" t="n">
-        <v>25439</v>
+        <v>27136</v>
       </c>
       <c r="K260" s="11" t="n">
-        <v>0.93199416281406</v>
+        <v>0.9359745156233039</v>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
@@ -15926,10 +15926,10 @@
         <v>2</v>
       </c>
       <c r="J261" s="9" t="n">
-        <v>25441</v>
+        <v>27138</v>
       </c>
       <c r="K261" s="11" t="n">
-        <v>0.9320794524860351</v>
+        <v>0.9360548133269495</v>
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
@@ -15987,10 +15987,10 @@
         <v>2</v>
       </c>
       <c r="J262" s="9" t="n">
-        <v>25444</v>
+        <v>27141</v>
       </c>
       <c r="K262" s="11" t="n">
-        <v>0.9321647421580102</v>
+        <v>0.9361351110305952</v>
       </c>
       <c r="L262" s="5" t="inlineStr">
         <is>
@@ -16048,10 +16048,10 @@
         <v>2</v>
       </c>
       <c r="J263" s="9" t="n">
-        <v>25446</v>
+        <v>27143</v>
       </c>
       <c r="K263" s="11" t="n">
-        <v>0.9322500318299852</v>
+        <v>0.9362154087342409</v>
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
@@ -16107,10 +16107,10 @@
         <v>14</v>
       </c>
       <c r="J264" s="9" t="n">
-        <v>25460</v>
+        <v>27157</v>
       </c>
       <c r="K264" s="11" t="n">
-        <v>0.9327556149370536</v>
+        <v>0.9366914002764701</v>
       </c>
       <c r="L264" s="5" t="inlineStr">
         <is>
@@ -16170,10 +16170,10 @@
         <v>9</v>
       </c>
       <c r="J265" s="9" t="n">
-        <v>25469</v>
+        <v>27166</v>
       </c>
       <c r="K265" s="11" t="n">
-        <v>0.9330853430503591</v>
+        <v>0.9370018295431414</v>
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
@@ -16233,10 +16233,10 @@
         <v>1</v>
       </c>
       <c r="J266" s="9" t="n">
-        <v>25470</v>
+        <v>27167</v>
       </c>
       <c r="K266" s="11" t="n">
-        <v>0.9331307722570812</v>
+        <v>0.9370445997976606</v>
       </c>
       <c r="L266" s="5" t="inlineStr">
         <is>
@@ -16296,10 +16296,10 @@
         <v>958</v>
       </c>
       <c r="J267" s="9" t="n">
-        <v>26428</v>
+        <v>28125</v>
       </c>
       <c r="K267" s="11" t="n">
-        <v>0.9682138435127828</v>
+        <v>0.9700742737714829</v>
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
@@ -16359,10 +16359,10 @@
         <v>1</v>
       </c>
       <c r="J268" s="9" t="n">
-        <v>26428</v>
+        <v>28125</v>
       </c>
       <c r="K268" s="11" t="n">
-        <v>0.9682420535846989</v>
+        <v>0.9701008327198537</v>
       </c>
       <c r="L268" s="5" t="inlineStr">
         <is>
@@ -16422,10 +16422,10 @@
         <v>4</v>
       </c>
       <c r="J269" s="9" t="n">
-        <v>26433</v>
+        <v>28129</v>
       </c>
       <c r="K269" s="11" t="n">
-        <v>0.9683959267042416</v>
+        <v>0.970245699710967</v>
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
@@ -16485,10 +16485,10 @@
         <v>3</v>
       </c>
       <c r="J270" s="9" t="n">
-        <v>26436</v>
+        <v>28132</v>
       </c>
       <c r="K270" s="11" t="n">
-        <v>0.9685058360753434</v>
+        <v>0.9703491761331907</v>
       </c>
       <c r="L270" s="5" t="inlineStr">
         <is>
@@ -16548,10 +16548,10 @@
         <v>4</v>
       </c>
       <c r="J271" s="9" t="n">
-        <v>26439</v>
+        <v>28136</v>
       </c>
       <c r="K271" s="11" t="n">
-        <v>0.9686340636749621</v>
+        <v>0.9704698986257851</v>
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
@@ -16611,10 +16611,10 @@
         <v>4</v>
       </c>
       <c r="J272" s="9" t="n">
-        <v>26443</v>
+        <v>28140</v>
       </c>
       <c r="K272" s="11" t="n">
-        <v>0.9687850058779419</v>
+        <v>0.970612006245639</v>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
@@ -16674,10 +16674,10 @@
         <v>2</v>
       </c>
       <c r="J273" s="9" t="n">
-        <v>26445</v>
+        <v>28142</v>
       </c>
       <c r="K273" s="11" t="n">
-        <v>0.9688406932926336</v>
+        <v>0.9706644342995657</v>
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
@@ -16737,10 +16737,10 @@
         <v>1</v>
       </c>
       <c r="J274" s="9" t="n">
-        <v>26445</v>
+        <v>28142</v>
       </c>
       <c r="K274" s="11" t="n">
-        <v>0.9688663388125573</v>
+        <v>0.9706885787980847</v>
       </c>
       <c r="L274" s="5" t="inlineStr">
         <is>
@@ -16798,10 +16798,10 @@
         <v>1</v>
       </c>
       <c r="J275" s="9" t="n">
-        <v>26446</v>
+        <v>28143</v>
       </c>
       <c r="K275" s="11" t="n">
-        <v>0.9688919843324811</v>
+        <v>0.9707127232966036</v>
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
@@ -16859,10 +16859,10 @@
         <v>66</v>
       </c>
       <c r="J276" s="9" t="n">
-        <v>26513</v>
+        <v>28210</v>
       </c>
       <c r="K276" s="11" t="n">
-        <v>0.9713283087252381</v>
+        <v>0.9730064506558967</v>
       </c>
       <c r="L276" s="5" t="inlineStr">
         <is>
@@ -16920,10 +16920,10 @@
         <v>2</v>
       </c>
       <c r="J277" s="9" t="n">
-        <v>26515</v>
+        <v>28212</v>
       </c>
       <c r="K277" s="11" t="n">
-        <v>0.9714052452850094</v>
+        <v>0.9730788841514534</v>
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
@@ -16981,10 +16981,10 @@
         <v>2</v>
       </c>
       <c r="J278" s="9" t="n">
-        <v>26517</v>
+        <v>28214</v>
       </c>
       <c r="K278" s="11" t="n">
-        <v>0.9714858454904841</v>
+        <v>0.9731547668610842</v>
       </c>
       <c r="L278" s="5" t="inlineStr">
         <is>
@@ -17063,10 +17063,10 @@
         <v>520</v>
       </c>
       <c r="J280" s="9" t="n">
-        <v>27037</v>
+        <v>28734</v>
       </c>
       <c r="K280" s="11" t="n">
-        <v>0.9905368031481333</v>
+        <v>0.9910906800465349</v>
       </c>
       <c r="L280" s="5" t="inlineStr">
         <is>
@@ -17116,10 +17116,10 @@
         <v>40</v>
       </c>
       <c r="J281" s="9" t="n">
-        <v>27077</v>
+        <v>28774</v>
       </c>
       <c r="K281" s="11" t="n">
-        <v>0.9920022614294909</v>
+        <v>0.992470365676185</v>
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
@@ -17171,10 +17171,10 @@
         <v>40</v>
       </c>
       <c r="J282" s="9" t="n">
-        <v>27117</v>
+        <v>28814</v>
       </c>
       <c r="K282" s="11" t="n">
-        <v>0.9934677197108486</v>
+        <v>0.993850051305835</v>
       </c>
       <c r="L282" s="5" t="inlineStr">
         <is>
@@ -17226,10 +17226,10 @@
         <v>40</v>
       </c>
       <c r="J283" s="9" t="n">
-        <v>27157</v>
+        <v>28854</v>
       </c>
       <c r="K283" s="11" t="n">
-        <v>0.9949331779922062</v>
+        <v>0.9952297369354851</v>
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
@@ -17285,10 +17285,10 @@
         <v>12</v>
       </c>
       <c r="J284" s="9" t="n">
-        <v>27169</v>
+        <v>28866</v>
       </c>
       <c r="K284" s="11" t="n">
-        <v>0.9953838064137236</v>
+        <v>0.9956539902666024</v>
       </c>
       <c r="L284" s="5" t="inlineStr">
         <is>
@@ -17342,10 +17342,10 @@
         <v>25</v>
       </c>
       <c r="J285" s="9" t="n">
-        <v>27194</v>
+        <v>28891</v>
       </c>
       <c r="K285" s="11" t="n">
-        <v>0.9962850632567585</v>
+        <v>0.9965024969288372</v>
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
@@ -17395,10 +17395,10 @@
         <v>37</v>
       </c>
       <c r="J286" s="9" t="n">
-        <v>27231</v>
+        <v>28928</v>
       </c>
       <c r="K286" s="11" t="n">
-        <v>0.9976369485213109</v>
+        <v>0.9977752569221894</v>
       </c>
       <c r="L286" s="5" t="inlineStr">
         <is>
@@ -17452,10 +17452,10 @@
         <v>7</v>
       </c>
       <c r="J287" s="9" t="n">
-        <v>27238</v>
+        <v>28934</v>
       </c>
       <c r="K287" s="11" t="n">
-        <v>0.9978860764291417</v>
+        <v>0.9980098034792299</v>
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
@@ -17513,10 +17513,10 @@
         <v>7</v>
       </c>
       <c r="J288" s="9" t="n">
-        <v>27244</v>
+        <v>28941</v>
       </c>
       <c r="K288" s="11" t="n">
-        <v>0.9981352043369724</v>
+        <v>0.9982443500362703</v>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
@@ -17570,10 +17570,10 @@
         <v>7</v>
       </c>
       <c r="J289" s="9" t="n">
-        <v>27251</v>
+        <v>28948</v>
       </c>
       <c r="K289" s="11" t="n">
-        <v>0.9983843322448033</v>
+        <v>0.9984788965933109</v>
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
@@ -17623,10 +17623,10 @@
         <v>7</v>
       </c>
       <c r="J290" s="9" t="n">
-        <v>27258</v>
+        <v>28955</v>
       </c>
       <c r="K290" s="11" t="n">
-        <v>0.998633460152634</v>
+        <v>0.9987134431503514</v>
       </c>
       <c r="L290" s="5" t="inlineStr">
         <is>
@@ -17678,10 +17678,10 @@
         <v>4</v>
       </c>
       <c r="J291" s="9" t="n">
-        <v>27262</v>
+        <v>28959</v>
       </c>
       <c r="K291" s="11" t="n">
-        <v>0.9987800059807698</v>
+        <v>0.9988514117133164</v>
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
@@ -17739,10 +17739,10 @@
         <v>13</v>
       </c>
       <c r="J292" s="9" t="n">
-        <v>27275</v>
+        <v>28971</v>
       </c>
       <c r="K292" s="11" t="n">
-        <v>0.9992434571622492</v>
+        <v>0.9992877372936932</v>
       </c>
       <c r="L292" s="5" t="inlineStr">
         <is>
@@ -17798,10 +17798,10 @@
         <v>1</v>
       </c>
       <c r="J293" s="9" t="n">
-        <v>27276</v>
+        <v>28973</v>
       </c>
       <c r="K293" s="11" t="n">
-        <v>0.9992898022803971</v>
+        <v>0.9993313698517309</v>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
@@ -17855,10 +17855,10 @@
         <v>1</v>
       </c>
       <c r="J294" s="9" t="n">
-        <v>27277</v>
+        <v>28974</v>
       </c>
       <c r="K294" s="11" t="n">
-        <v>0.999336147398545</v>
+        <v>0.9993750024097685</v>
       </c>
       <c r="L294" s="5" t="inlineStr">
         <is>
@@ -17912,10 +17912,10 @@
         <v>10</v>
       </c>
       <c r="J295" s="9" t="n">
-        <v>27287</v>
+        <v>28984</v>
       </c>
       <c r="K295" s="11" t="n">
-        <v>0.9997069083437284</v>
+        <v>0.99972406287407</v>
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>8</v>
       </c>
       <c r="J296" s="9" t="n">
-        <v>27295</v>
+        <v>28992</v>
       </c>
       <c r="K296" s="11" t="n">
         <v>1</v>
@@ -18121,13 +18121,13 @@
         <v>228</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.008353112203738489</v>
+        <v>0.007864208089005327</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>228</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.008353112203738489</v>
+        <v>0.007864208089005327</v>
       </c>
       <c r="H5" s="20" t="n">
         <v>228</v>
@@ -18155,13 +18155,13 @@
         <v>3456</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>0.1266155955092992</v>
+        <v>0.119204838401765</v>
       </c>
       <c r="F6" s="18" t="n">
         <v>3684</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.1349687077130377</v>
+        <v>0.1270690464907703</v>
       </c>
       <c r="H6" s="20" t="n">
         <v>192</v>
@@ -18189,13 +18189,13 @@
         <v>2625</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>0.09617069971409443</v>
+        <v>0.09054186944578502</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>6309</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.2311394074271321</v>
+        <v>0.2176109159365553</v>
       </c>
       <c r="H7" s="20" t="n">
         <v>125</v>
@@ -18223,13 +18223,13 @@
         <v>2953</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.1082021122040406</v>
+        <v>0.101869088465212</v>
       </c>
       <c r="F8" s="18" t="n">
         <v>9262</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>0.3393415196311727</v>
+        <v>0.3194800044017673</v>
       </c>
       <c r="H8" s="20" t="n">
         <v>101.8</v>
@@ -18254,19 +18254,19 @@
         <v>14</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.0223079348844662</v>
+        <v>0.02187146644402754</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>9871</v>
+        <v>9896</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.3616494545156389</v>
+        <v>0.3413514708457948</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>43.5</v>
+        <v>45.3</v>
       </c>
       <c r="I9" s="17" t="n">
         <v>4</v>
@@ -18291,13 +18291,13 @@
         <v>796</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>0.02917922037043287</v>
+        <v>0.0274713729770475</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>10668</v>
+        <v>10693</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.3908286748860718</v>
+        <v>0.3688228438228424</v>
       </c>
       <c r="H10" s="20" t="n">
         <v>41.9</v>
@@ -18322,19 +18322,19 @@
         <v>91</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>2289</v>
+        <v>2814</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.08386312002845168</v>
+        <v>0.09706088404588152</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>12957</v>
+        <v>13507</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.4746917949145235</v>
+        <v>0.4658837278687239</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>25.2</v>
+        <v>30.9</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>5</v>
@@ -18356,19 +18356,19 @@
         <v>173</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>4815</v>
+        <v>5613</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>0.1764028075459993</v>
+        <v>0.1936043859806443</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>17772</v>
+        <v>19120</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.6510946024605228</v>
+        <v>0.6594881138493682</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>27.8</v>
+        <v>32.4</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>6</v>
@@ -18390,19 +18390,19 @@
         <v>17</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.009900690640982188</v>
+        <v>0.01276209207426303</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>18042</v>
+        <v>19490</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.660995293101505</v>
+        <v>0.6722502059236313</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>15.9</v>
+        <v>21.8</v>
       </c>
       <c r="I13" s="17" t="inlineStr"/>
       <c r="J13" s="21" t="inlineStr"/>
@@ -18420,19 +18420,19 @@
         <v>94</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1252</v>
+        <v>1420</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.04588279339529842</v>
+        <v>0.04897883985257704</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>19294</v>
+        <v>20910</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>0.7068780864968035</v>
+        <v>0.7212290457762083</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="I14" s="17" t="inlineStr"/>
       <c r="J14" s="21" t="inlineStr"/>
@@ -18450,19 +18450,19 @@
         <v>2</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.0004561344734602473</v>
+        <v>0.0009657799407550402</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>19307</v>
+        <v>20938</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.7073342209702638</v>
+        <v>0.7221948257169634</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="I15" s="17" t="inlineStr"/>
       <c r="J15" s="21" t="inlineStr"/>
@@ -18480,16 +18480,16 @@
         <v>245</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>2635</v>
+        <v>2647</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>0.09651975810266802</v>
+        <v>0.09130196125391972</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>21941</v>
+        <v>23585</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.8038539790729317</v>
+        <v>0.8134967869708831</v>
       </c>
       <c r="H16" s="20" t="n">
         <v>10.8</v>
@@ -18510,19 +18510,19 @@
         <v>27</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.006675603085138032</v>
+        <v>0.009312878000137888</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>22124</v>
+        <v>23855</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.8105295821580697</v>
+        <v>0.8228096649710209</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="I17" s="17" t="inlineStr"/>
       <c r="J17" s="21" t="inlineStr"/>
@@ -18540,19 +18540,19 @@
         <v>161</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>690</v>
+        <v>650</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>0.02526363142582664</v>
+        <v>0.02242334069588756</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>22813</v>
+        <v>24505</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>0.8357932135838964</v>
+        <v>0.8452330056669085</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="17" t="inlineStr"/>
       <c r="J18" s="21" t="inlineStr"/>
@@ -18573,13 +18573,13 @@
         <v>626</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.02293991757180199</v>
+        <v>0.02159725392513458</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>23439</v>
+        <v>25131</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.8587331311556985</v>
+        <v>0.8668302595920431</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>3.3</v>
@@ -18600,16 +18600,16 @@
         <v>541</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>0.04822020449327102</v>
+        <v>0.04557274095437847</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>24755</v>
+        <v>26452</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>0.9069533356489694</v>
+        <v>0.9124030005464215</v>
       </c>
       <c r="H20" s="20" t="n">
         <v>2.4</v>
@@ -18633,13 +18633,13 @@
         <v>325</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.01189976966450048</v>
+        <v>0.01119959809868434</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>25080</v>
+        <v>26777</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.9188531053134699</v>
+        <v>0.923602598645106</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>2.6</v>
@@ -18663,13 +18663,13 @@
         <v>1355</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>0.04965273076187326</v>
+        <v>0.04674657748808472</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>26436</v>
+        <v>28132</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.968505836075343</v>
+        <v>0.9703491761331906</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>1.4</v>
@@ -18693,13 +18693,13 @@
         <v>79</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.00289940920966607</v>
+        <v>0.002729708018262638</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>26515</v>
+        <v>28212</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.9714052452850092</v>
+        <v>0.9730788841514533</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>0.8</v>
@@ -18723,13 +18723,13 @@
         <v>2</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>8.060020547466964e-05</v>
+        <v>7.588270963075316e-05</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>26517</v>
+        <v>28214</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.9714858454904838</v>
+        <v>0.973154766861084</v>
       </c>
       <c r="H24" s="20" t="n">
         <v>1.1</v>
@@ -18753,13 +18753,13 @@
         <v>778</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.02851415450951606</v>
+        <v>0.02684523313891598</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>27295</v>
+        <v>28992</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>13.9</v>
@@ -18777,21 +18777,21 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>— Ду200 и выше — 9.26 т, это 34% всего веса. Это и есть первый слой на полу, с него начинается погрузка и им определяется, влезет груз или нет.</t>
+          <t>— Ду200 и выше — 9.26 т, это 32% всего веса. Это и есть первый слой на полу, с него начинается погрузка и им определяется, влезет груз или нет.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>— Ду100-150 — 3.69 т, 14%. Идет рядом на пол или в низ ящиков.</t>
+          <t>— Ду100-150 — 4.24 т, 15%. Идет рядом на пол или в низ ящиков.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>— Ду80 и меньше — 13.56 т, 50%. Вся эта мелочь уходит в ящики, и ее место в контейнере сверху.</t>
+          <t>— Ду80 и меньше — 14.71 т, 51%. Вся эта мелочь уходит в ящики, и ее место в контейнере сверху.</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19103,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>540</v>
+        <v>384</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>53</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1015</v>
+        <v>1696</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>65</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>762</v>
+        <v>1560</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>7</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>7</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>16</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>16</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>8</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Арматура_по_размеру.xlsx
+++ b/outputs/marine_equipment/Арматура_по_размеру.xlsx
@@ -694,7 +694,7 @@
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G6" s="9" t="n">
@@ -814,7 +814,7 @@
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
@@ -873,7 +873,7 @@
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
@@ -951,7 +951,7 @@
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G11" s="9" t="n">
@@ -1008,7 +1008,7 @@
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
@@ -1067,7 +1067,7 @@
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G13" s="9" t="n">
@@ -1126,7 +1126,7 @@
       <c r="E14" s="8" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G14" s="9" t="n">
@@ -1185,7 +1185,7 @@
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G15" s="9" t="n">
@@ -1242,7 +1242,7 @@
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G16" s="9" t="n">
@@ -1385,7 +1385,7 @@
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G19" s="9" t="n">
@@ -1442,7 +1442,7 @@
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G20" s="9" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G21" s="9" t="n">
@@ -1560,7 +1560,7 @@
       <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G22" s="9" t="n">
@@ -1745,7 +1745,7 @@
       <c r="E25" s="8" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G25" s="9" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G26" s="9" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G27" s="9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G28" s="9" t="n">
@@ -2054,7 +2054,7 @@
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G30" s="9" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G31" s="9" t="n">
@@ -2174,7 +2174,7 @@
       <c r="E32" s="8" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G32" s="9" t="n">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G33" s="9" t="n">
@@ -2296,7 +2296,7 @@
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G34" s="9" t="n">
@@ -2351,7 +2351,7 @@
       <c r="E35" s="8" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G35" s="9" t="n">
@@ -2408,7 +2408,7 @@
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G36" s="9" t="n">
@@ -2465,7 +2465,7 @@
       <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G37" s="9" t="n">
@@ -2522,7 +2522,7 @@
       <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G38" s="9" t="n">
@@ -2636,7 +2636,7 @@
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G40" s="9" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G41" s="9" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G42" s="9" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G43" s="9" t="n">
@@ -2943,7 +2943,7 @@
       <c r="E45" s="8" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G45" s="9" t="n">
@@ -3000,7 +3000,7 @@
       <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G46" s="9" t="n">
@@ -3078,7 +3078,7 @@
       <c r="E48" s="8" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G48" s="9" t="n">
@@ -3137,7 +3137,7 @@
       <c r="E49" s="8" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G49" s="9" t="n">
@@ -3192,7 +3192,7 @@
       <c r="E50" s="8" t="inlineStr"/>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G50" s="9" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G51" s="9" t="n">
@@ -3308,7 +3308,7 @@
       <c r="E52" s="8" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G52" s="9" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G53" s="9" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G54" s="9" t="n">
@@ -3548,7 +3548,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G56" s="9" t="n">
@@ -3605,7 +3605,7 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G57" s="9" t="n">
@@ -3662,7 +3662,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G58" s="9" t="n">
@@ -3719,7 +3719,7 @@
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G59" s="9" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G60" s="9" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G61" s="9" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G63" s="9" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G64" s="9" t="n">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G65" s="9" t="n">
@@ -4142,7 +4142,7 @@
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G66" s="9" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G68" s="9" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G69" s="9" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G70" s="9" t="n">
@@ -4443,7 +4443,7 @@
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G71" s="9" t="n">
@@ -4500,7 +4500,7 @@
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G72" s="9" t="n">
@@ -4557,7 +4557,7 @@
       <c r="E73" s="8" t="inlineStr"/>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G73" s="9" t="n">
@@ -4614,7 +4614,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G74" s="9" t="n">
@@ -4671,7 +4671,7 @@
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G75" s="9" t="n">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G76" s="9" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G77" s="9" t="n">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G78" s="9" t="n">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G79" s="9" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G80" s="9" t="n">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G81" s="9" t="n">
@@ -5098,7 +5098,7 @@
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G82" s="9" t="n">
@@ -5155,7 +5155,7 @@
       <c r="E83" s="8" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G83" s="9" t="n">
@@ -5212,7 +5212,7 @@
       <c r="E84" s="8" t="inlineStr"/>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G84" s="9" t="n">
@@ -5271,7 +5271,7 @@
       <c r="E85" s="8" t="inlineStr"/>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G85" s="9" t="n">
@@ -5326,7 +5326,7 @@
       <c r="E86" s="8" t="inlineStr"/>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G86" s="9" t="n">
@@ -5381,7 +5381,7 @@
       <c r="E87" s="8" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G87" s="9" t="n">
@@ -5440,7 +5440,7 @@
       <c r="E88" s="8" t="inlineStr"/>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G88" s="9" t="n">
@@ -5497,7 +5497,7 @@
       <c r="E89" s="8" t="inlineStr"/>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G89" s="9" t="n">
@@ -5556,7 +5556,7 @@
       <c r="E90" s="8" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G90" s="9" t="n">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G91" s="9" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G92" s="9" t="n">
@@ -5737,7 +5737,7 @@
       <c r="E93" s="8" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G93" s="9" t="n">
@@ -5794,7 +5794,7 @@
       <c r="E94" s="8" t="inlineStr"/>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G94" s="9" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G95" s="9" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G96" s="9" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G97" s="9" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G98" s="9" t="n">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G99" s="9" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G100" s="9" t="n">
@@ -6221,7 +6221,7 @@
       <c r="E101" s="8" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G101" s="9" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G102" s="9" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G103" s="9" t="n">
@@ -6394,7 +6394,7 @@
       <c r="E104" s="8" t="inlineStr"/>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G104" s="9" t="n">
@@ -6451,7 +6451,7 @@
       <c r="E105" s="8" t="inlineStr"/>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G105" s="9" t="n">
@@ -6508,7 +6508,7 @@
       <c r="E106" s="8" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G106" s="9" t="n">
@@ -6565,7 +6565,7 @@
       <c r="E107" s="8" t="inlineStr"/>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G107" s="9" t="n">
@@ -6679,7 +6679,7 @@
       <c r="E109" s="8" t="inlineStr"/>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G109" s="9" t="n">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G111" s="9" t="n">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G113" s="9" t="n">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G114" s="9" t="n">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G116" s="9" t="n">
@@ -7129,7 +7129,7 @@
       <c r="E117" s="8" t="inlineStr"/>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G117" s="9" t="n">
@@ -7186,7 +7186,7 @@
       <c r="E118" s="8" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G118" s="9" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G119" s="9" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G120" s="9" t="n">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G122" s="9" t="n">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G123" s="9" t="n">
@@ -7548,7 +7548,7 @@
       <c r="E124" s="8" t="inlineStr"/>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G124" s="9" t="n">
@@ -7605,7 +7605,7 @@
       <c r="E125" s="8" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G125" s="9" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G126" s="9" t="n">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G127" s="9" t="n">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G129" s="9" t="n">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G130" s="9" t="n">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G131" s="9" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G132" s="9" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G133" s="9" t="n">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G134" s="9" t="n">
@@ -8215,7 +8215,7 @@
       <c r="E135" s="8" t="inlineStr"/>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G135" s="9" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G136" s="9" t="n">
@@ -8333,7 +8333,7 @@
       <c r="E137" s="8" t="inlineStr"/>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G137" s="9" t="n">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G138" s="9" t="n">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G139" s="9" t="n">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G140" s="9" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G141" s="9" t="n">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G142" s="9" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G143" s="9" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G144" s="9" t="n">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G145" s="9" t="n">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G146" s="9" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G148" s="9" t="n">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G149" s="9" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G150" s="9" t="n">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G151" s="9" t="n">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G152" s="9" t="n">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G153" s="9" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G154" s="9" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G155" s="9" t="n">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G156" s="9" t="n">
@@ -9563,7 +9563,7 @@
       <c r="E157" s="8" t="inlineStr"/>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G157" s="9" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G158" s="9" t="n">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G159" s="9" t="n">
@@ -9742,7 +9742,7 @@
       <c r="E160" s="8" t="inlineStr"/>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G160" s="9" t="n">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G161" s="9" t="n">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G163" s="9" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G165" s="9" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G166" s="9" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G167" s="9" t="n">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G168" s="9" t="n">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G169" s="9" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G170" s="9" t="n">
@@ -10425,7 +10425,7 @@
       <c r="E171" s="8" t="inlineStr"/>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G171" s="9" t="n">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G172" s="9" t="n">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G173" s="9" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G174" s="9" t="n">
@@ -10665,7 +10665,7 @@
       <c r="E175" s="8" t="inlineStr"/>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G175" s="9" t="n">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G176" s="9" t="n">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G177" s="9" t="n">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G178" s="9" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G179" s="9" t="n">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G180" s="9" t="n">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G181" s="9" t="n">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G182" s="9" t="n">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G183" s="9" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G184" s="9" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G185" s="9" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G186" s="9" t="n">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G187" s="9" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G188" s="9" t="n">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G189" s="9" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G190" s="9" t="n">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G191" s="9" t="n">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G192" s="9" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G193" s="9" t="n">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G194" s="9" t="n">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G195" s="9" t="n">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G196" s="9" t="n">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G197" s="9" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G198" s="9" t="n">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G199" s="9" t="n">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G200" s="9" t="n">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G201" s="9" t="n">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G202" s="9" t="n">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G203" s="9" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G204" s="9" t="n">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G205" s="9" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G206" s="9" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G207" s="9" t="n">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G208" s="9" t="n">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G209" s="9" t="n">
@@ -12802,7 +12802,7 @@
       <c r="E210" s="8" t="inlineStr"/>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G210" s="9" t="n">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G211" s="9" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G212" s="9" t="n">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G213" s="9" t="n">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G214" s="9" t="n">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G215" s="9" t="n">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G216" s="9" t="n">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G217" s="9" t="n">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G218" s="9" t="n">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G219" s="9" t="n">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G220" s="9" t="n">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G221" s="9" t="n">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G222" s="9" t="n">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G223" s="9" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G224" s="9" t="n">
@@ -13717,7 +13717,7 @@
       <c r="E225" s="8" t="inlineStr"/>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G225" s="9" t="n">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G226" s="9" t="n">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G227" s="9" t="n">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G228" s="9" t="n">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G229" s="9" t="n">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G230" s="9" t="n">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G231" s="9" t="n">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G232" s="9" t="n">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G233" s="9" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G234" s="9" t="n">
@@ -14323,7 +14323,7 @@
       <c r="E235" s="8" t="inlineStr"/>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G235" s="9" t="n">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G236" s="9" t="n">
@@ -14443,7 +14443,7 @@
       <c r="E237" s="8" t="inlineStr"/>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G237" s="9" t="n">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G239" s="9" t="n">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G242" s="9" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G243" s="9" t="n">
@@ -14876,7 +14876,7 @@
       <c r="E244" s="8" t="inlineStr"/>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G244" s="9" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G245" s="9" t="n">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G246" s="9" t="n">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G247" s="9" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G248" s="9" t="n">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G249" s="9" t="n">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G250" s="9" t="n">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G252" s="9" t="n">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G253" s="9" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G254" s="9" t="n">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G255" s="9" t="n">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G257" s="9" t="n">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G258" s="9" t="n">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G259" s="9" t="n">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G260" s="9" t="n">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G261" s="9" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G262" s="9" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G263" s="9" t="n">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G264" s="9" t="n">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G265" s="9" t="n">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G266" s="9" t="n">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G267" s="9" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G268" s="9" t="n">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G269" s="9" t="n">
@@ -16472,7 +16472,7 @@
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G270" s="9" t="n">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G271" s="9" t="n">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G272" s="9" t="n">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G273" s="9" t="n">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G274" s="9" t="n">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G275" s="9" t="n">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G276" s="9" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G277" s="9" t="n">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G278" s="9" t="n">
@@ -17103,7 +17103,7 @@
       <c r="E281" s="8" t="inlineStr"/>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G281" s="9" t="n">
@@ -17158,7 +17158,7 @@
       <c r="E282" s="8" t="inlineStr"/>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G282" s="9" t="n">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G284" s="9" t="n">
@@ -17329,7 +17329,7 @@
       <c r="E285" s="8" t="inlineStr"/>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G285" s="9" t="n">
@@ -17382,7 +17382,7 @@
       <c r="E286" s="8" t="inlineStr"/>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G286" s="9" t="n">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G287" s="9" t="n">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G288" s="9" t="n">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G289" s="9" t="n">
@@ -17610,7 +17610,7 @@
       <c r="E290" s="8" t="inlineStr"/>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G290" s="9" t="n">
@@ -17665,7 +17665,7 @@
       <c r="E291" s="8" t="inlineStr"/>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G291" s="9" t="n">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G292" s="9" t="n">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G293" s="9" t="n">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G295" s="9" t="n">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G296" s="9" t="n">
